--- a/artfynd/A 32997-2019 artfynd.xlsx
+++ b/artfynd/A 32997-2019 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 32997-2019 artfynd.xlsx
+++ b/artfynd/A 32997-2019 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -792,137 +792,6 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>81780100</v>
-      </c>
-      <c r="B3" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>Mariero, 450 m SV , Sk</t>
-        </is>
-      </c>
-      <c r="Q3" t="n">
-        <v>416428.3620834564</v>
-      </c>
-      <c r="R3" t="n">
-        <v>6248759.532430399</v>
-      </c>
-      <c r="S3" t="n">
-        <v>10</v>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>Skåne</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>Hässleholm</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>Skåne</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>Vittsjö</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>M-Hlm-0460</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>2020-01-08</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>2020-01-08</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Förgäves eftersökt två gånger 2020. Biotop lämplig för knärot finns kvar inom det diffust angivna koordinatområdet.</t>
-        </is>
-      </c>
-      <c r="AD3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AE3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF3" t="inlineStr"/>
-      <c r="AG3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT3" t="inlineStr"/>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>Charlotte Wigermo</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>Crister Albinsson</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
         <is>
           <t>Floraväkteri Sverige</t>
         </is>
